--- a/config/generated/templates/UniverseBindings.xlsx
+++ b/config/generated/templates/UniverseBindings.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="132">
   <si>
     <t>@table</t>
   </si>
@@ -189,7 +189,7 @@
     <t>UniverseEncounterMember</t>
   </si>
   <si>
-    <t>6acf292c31949231</t>
+    <t>766b31b8036f726c</t>
   </si>
   <si>
     <t>group_id</t>
@@ -219,145 +219,145 @@
     <t>ref&lt;UniverseEncounterGroup.id&gt;</t>
   </si>
   <si>
+    <t>optional&lt;list&lt;string&gt;&gt;</t>
+  </si>
+  <si>
+    <t>range=1..1000</t>
+  </si>
+  <si>
+    <t>range=1..200</t>
+  </si>
+  <si>
+    <t>range=0..100</t>
+  </si>
+  <si>
+    <t>parser=split;separator=|;length=0..64</t>
+  </si>
+  <si>
+    <t>UniverseEncounterWave</t>
+  </si>
+  <si>
+    <t>8f77e125b36f4f92</t>
+  </si>
+  <si>
+    <t>member_id</t>
+  </si>
+  <si>
+    <t>ref&lt;UniverseEncounterMember.id&gt;</t>
+  </si>
+  <si>
+    <t>range=1..100</t>
+  </si>
+  <si>
+    <t>UniverseEncounterWaveEnemy</t>
+  </si>
+  <si>
+    <t>0c7ec3730b10fff7</t>
+  </si>
+  <si>
+    <t>wave_id</t>
+  </si>
+  <si>
+    <t>slot</t>
+  </si>
+  <si>
+    <t>source_monster_id</t>
+  </si>
+  <si>
+    <t>enemy_variant_stable_key</t>
+  </si>
+  <si>
+    <t>ref&lt;UniverseEncounterWave.id&gt;</t>
+  </si>
+  <si>
+    <t>range=1..32</t>
+  </si>
+  <si>
+    <t>UniverseEncounterPool</t>
+  </si>
+  <si>
+    <t>a22b7cefcea09ab8</t>
+  </si>
+  <si>
+    <t>room_id</t>
+  </si>
+  <si>
+    <t>domain_kind</t>
+  </si>
+  <si>
+    <t>map_entrance</t>
+  </si>
+  <si>
+    <t>selection_policy</t>
+  </si>
+  <si>
+    <t>source_primary_condition_key</t>
+  </si>
+  <si>
+    <t>ref&lt;UniverseRoom.id&gt;</t>
+  </si>
+  <si>
+    <t>enum&lt;UniverseDomainKind&gt;</t>
+  </si>
+  <si>
+    <t>enum&lt;UniverseSelectionPolicy&gt;</t>
+  </si>
+  <si>
+    <t>UniverseEncounterPoolGroup</t>
+  </si>
+  <si>
+    <t>9247a01d952a7f19</t>
+  </si>
+  <si>
+    <t>condition_key</t>
+  </si>
+  <si>
+    <t>ref&lt;UniverseEncounterPool.id&gt;</t>
+  </si>
+  <si>
+    <t>UniverseEncounterPoolFixed</t>
+  </si>
+  <si>
+    <t>2b08b493238e08d3</t>
+  </si>
+  <si>
+    <t>source_content_id</t>
+  </si>
+  <si>
+    <t>UniverseMechanicRule</t>
+  </si>
+  <si>
+    <t>a0fee1bbce49b81b</t>
+  </si>
+  <si>
+    <t>source_record_stable_key</t>
+  </si>
+  <si>
+    <t>source_file</t>
+  </si>
+  <si>
+    <t>rule_kind</t>
+  </si>
+  <si>
+    <t>native_handler_stable_key</t>
+  </si>
+  <si>
+    <t>source_binding_key</t>
+  </si>
+  <si>
+    <t>parameter_values_json</t>
+  </si>
+  <si>
+    <t>mechanic_tags</t>
+  </si>
+  <si>
+    <t>approximation_replacement_condition</t>
+  </si>
+  <si>
+    <t>enum&lt;UniverseMechanicRuleKind&gt;</t>
+  </si>
+  <si>
     <t>list&lt;string&gt;</t>
-  </si>
-  <si>
-    <t>range=1..1000</t>
-  </si>
-  <si>
-    <t>range=1..200</t>
-  </si>
-  <si>
-    <t>range=0..100</t>
-  </si>
-  <si>
-    <t>parser=split;separator=|;length=0..64</t>
-  </si>
-  <si>
-    <t>UniverseEncounterWave</t>
-  </si>
-  <si>
-    <t>8f77e125b36f4f92</t>
-  </si>
-  <si>
-    <t>member_id</t>
-  </si>
-  <si>
-    <t>ref&lt;UniverseEncounterMember.id&gt;</t>
-  </si>
-  <si>
-    <t>range=1..100</t>
-  </si>
-  <si>
-    <t>UniverseEncounterWaveEnemy</t>
-  </si>
-  <si>
-    <t>7a0730a35ef59981</t>
-  </si>
-  <si>
-    <t>wave_id</t>
-  </si>
-  <si>
-    <t>slot</t>
-  </si>
-  <si>
-    <t>source_monster_id</t>
-  </si>
-  <si>
-    <t>enemy_variant_id</t>
-  </si>
-  <si>
-    <t>ref&lt;UniverseEncounterWave.id&gt;</t>
-  </si>
-  <si>
-    <t>ref&lt;EnemyVariant.id&gt;</t>
-  </si>
-  <si>
-    <t>range=1..32</t>
-  </si>
-  <si>
-    <t>UniverseEncounterPool</t>
-  </si>
-  <si>
-    <t>a22b7cefcea09ab8</t>
-  </si>
-  <si>
-    <t>room_id</t>
-  </si>
-  <si>
-    <t>domain_kind</t>
-  </si>
-  <si>
-    <t>map_entrance</t>
-  </si>
-  <si>
-    <t>selection_policy</t>
-  </si>
-  <si>
-    <t>source_primary_condition_key</t>
-  </si>
-  <si>
-    <t>ref&lt;UniverseRoom.id&gt;</t>
-  </si>
-  <si>
-    <t>enum&lt;UniverseDomainKind&gt;</t>
-  </si>
-  <si>
-    <t>enum&lt;UniverseSelectionPolicy&gt;</t>
-  </si>
-  <si>
-    <t>UniverseEncounterPoolGroup</t>
-  </si>
-  <si>
-    <t>9247a01d952a7f19</t>
-  </si>
-  <si>
-    <t>condition_key</t>
-  </si>
-  <si>
-    <t>ref&lt;UniverseEncounterPool.id&gt;</t>
-  </si>
-  <si>
-    <t>UniverseEncounterPoolFixed</t>
-  </si>
-  <si>
-    <t>2b08b493238e08d3</t>
-  </si>
-  <si>
-    <t>source_content_id</t>
-  </si>
-  <si>
-    <t>UniverseMechanicRule</t>
-  </si>
-  <si>
-    <t>a0fee1bbce49b81b</t>
-  </si>
-  <si>
-    <t>source_record_stable_key</t>
-  </si>
-  <si>
-    <t>source_file</t>
-  </si>
-  <si>
-    <t>rule_kind</t>
-  </si>
-  <si>
-    <t>native_handler_stable_key</t>
-  </si>
-  <si>
-    <t>source_binding_key</t>
-  </si>
-  <si>
-    <t>parameter_values_json</t>
-  </si>
-  <si>
-    <t>mechanic_tags</t>
-  </si>
-  <si>
-    <t>approximation_replacement_condition</t>
-  </si>
-  <si>
-    <t>enum&lt;UniverseMechanicRuleKind&gt;</t>
   </si>
   <si>
     <t>length=2..16000</t>
@@ -1025,7 +1025,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="24" customHeight="1">
@@ -1063,28 +1063,28 @@
         <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>45</v>
@@ -1110,28 +1110,28 @@
         <v>11</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>45</v>
@@ -1163,7 +1163,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>36</v>
@@ -1175,7 +1175,7 @@
         <v>18</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>36</v>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -2098,7 +2098,7 @@
     <col min="8" max="8" width="14.7109375" style="5" customWidth="1"/>
     <col min="9" max="9" width="12.7109375" style="5" customWidth="1"/>
     <col min="10" max="10" width="16.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="17.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="22.7109375" style="5" customWidth="1"/>
     <col min="12" max="12" width="16.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2502,7 +2502,7 @@
     <col min="2" max="2" width="29.7109375" style="5" customWidth="1"/>
     <col min="3" max="4" width="12.7109375" style="5" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" style="5" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -2592,7 +2592,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>39</v>
@@ -2629,7 +2629,9 @@
       <c r="E6" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="5"/>
+      <c r="F6" s="5" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
@@ -2673,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -2697,7 +2699,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="24" customHeight="1">
@@ -2711,19 +2713,19 @@
         <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>45</v>
@@ -2749,19 +2751,19 @@
         <v>11</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>45</v>
@@ -2787,16 +2789,16 @@
         <v>18</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>92</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>18</v>
@@ -2935,7 +2937,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -2957,7 +2959,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1">
@@ -2971,7 +2973,7 @@
         <v>31</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>55</v>
@@ -2991,7 +2993,7 @@
         <v>31</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>55</v>
@@ -3005,7 +3007,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>17</v>
@@ -3094,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -3116,7 +3118,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1">
@@ -3130,10 +3132,10 @@
         <v>31</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3147,10 +3149,10 @@
         <v>31</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3158,7 +3160,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>17</v>

--- a/config/generated/templates/UniverseBindings.xlsx
+++ b/config/generated/templates/UniverseBindings.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="131">
   <si>
     <t>@table</t>
   </si>
@@ -327,7 +327,7 @@
     <t>UniverseMechanicRule</t>
   </si>
   <si>
-    <t>a0fee1bbce49b81b</t>
+    <t>a9046b0aa5a2ae4e</t>
   </si>
   <si>
     <t>source_record_stable_key</t>
@@ -355,9 +355,6 @@
   </si>
   <si>
     <t>enum&lt;UniverseMechanicRuleKind&gt;</t>
-  </si>
-  <si>
-    <t>list&lt;string&gt;</t>
   </si>
   <si>
     <t>length=2..16000</t>
@@ -1014,7 +1011,7 @@
     <col min="7" max="7" width="25.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="18.7109375" style="5" customWidth="1"/>
     <col min="9" max="9" width="21.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="5" customWidth="1"/>
     <col min="11" max="11" width="32.7109375" style="5" customWidth="1"/>
     <col min="12" max="14" width="12.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="13.7109375" style="5" customWidth="1"/>
@@ -1175,7 +1172,7 @@
         <v>18</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>36</v>
@@ -1260,17 +1257,17 @@
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>68</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N6" s="5" t="s">
         <v>52</v>
@@ -1333,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -1357,7 +1354,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1">
@@ -1371,25 +1368,25 @@
         <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1403,25 +1400,25 @@
         <v>11</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>120</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1435,7 +1432,7 @@
         <v>18</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>18</v>
@@ -1506,10 +1503,10 @@
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="42" customHeight="1">
@@ -1563,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -1585,7 +1582,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1">
@@ -1593,16 +1590,16 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1610,16 +1607,16 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1627,16 +1624,16 @@
         <v>16</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:10">

--- a/config/generated/templates/UniverseBindings.xlsx
+++ b/config/generated/templates/UniverseBindings.xlsx
@@ -987,8 +987,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Blessing, Curio, Occurrence, Encounter, Shop" promptTitle="UniversePoolKind enum" prompt="Select a value from the dropdown." sqref="D8:D1007">
-      <formula1>"Blessing,Curio,Occurrence,Encounter,Shop"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Blessing, Curio, Occurrence, Encounter, Shop, TrailblazeBonus" promptTitle="UniversePoolKind enum" prompt="Select a value from the dropdown." sqref="D8:D1007">
+      <formula1>"Blessing,Curio,Occurrence,Encounter,Shop,TrailblazeBonus"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="F8:F1007">
       <formula1>"true,false"</formula1>
